--- a/data/trans_dic/P25C$productsfarma_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,35</t>
+          <t>0,0; 9,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,36</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,38</t>
+          <t>0,3; 10,57</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,0</t>
+          <t>0,73; 8,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,87</t>
+          <t>1,03; 8,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,42</t>
+          <t>0,95; 6,62</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,22</t>
+          <t>0,58; 5,03</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 26,91</t>
+          <t>8,51; 25,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,84</t>
+          <t>2,31; 10,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 18,7</t>
+          <t>7,13; 17,84</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 9,51</t>
+          <t>0,81; 9,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,03</t>
+          <t>0,82; 5,23</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,73</t>
+          <t>0,97; 4,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,38</t>
+          <t>1,81; 5,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,16</t>
+          <t>1,45; 4,16</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5871</t>
+          <t>0; 4520</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 2880</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172; 5596</t>
+          <t>177; 6303</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>830; 8840</t>
+          <t>810; 9446</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>678; 5808</t>
+          <t>675; 5838</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2209; 11302</t>
+          <t>1680; 11654</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5257</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4613</t>
+          <t>0; 4377</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>651; 6175</t>
+          <t>687; 5953</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8096; 25427</t>
+          <t>8044; 23623</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1145; 6307</t>
+          <t>1346; 6378</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10772; 28544</t>
+          <t>10887; 27236</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 753</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 941</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1092</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6148</t>
+          <t>0; 6679</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>628; 9018</t>
+          <t>773; 8674</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1652; 10893</t>
+          <t>1773; 11325</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 11053</t>
+          <t>0; 10855</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 1175</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8767</t>
+          <t>0; 9794</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8387; 40205</t>
+          <t>8218; 38177</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5844; 18144</t>
+          <t>6096; 16891</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15660; 49324</t>
+          <t>17238; 49429</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$productsfarma_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,51</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 28,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 10,57</t>
+          <t>0,89; 9,83</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,55</t>
+          <t>0,75; 7,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,92</t>
+          <t>1,02; 8,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,62</t>
+          <t>1,09; 5,99</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 9,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,03</t>
+          <t>0,57; 5,36</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 25,0</t>
+          <t>7,54; 23,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,96</t>
+          <t>1,96; 10,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 17,84</t>
+          <t>6,24; 16,3</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 9,15</t>
+          <t>1,23; 11,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,23</t>
+          <t>0,89; 4,82</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,58; 6,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,42; 4,24</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,49</t>
+          <t>2,33; 5,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,01</t>
+          <t>1,76; 5,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,16</t>
+          <t>2,49; 4,97</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1985</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4520</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2880</t>
+          <t>0; 3542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177; 6303</t>
+          <t>556; 6171</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5385</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>810; 9446</t>
+          <t>890; 8871</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>675; 5838</t>
+          <t>683; 5787</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1680; 11654</t>
+          <t>2019; 11103</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>911</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2298</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 4955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>687; 5953</t>
+          <t>674; 6288</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>18130</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8044; 23623</t>
+          <t>8097; 24983</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1346; 6378</t>
+          <t>1274; 6858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10887; 27236</t>
+          <t>10763; 28122</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5762</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6679</t>
+          <t>0; 6536</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>773; 8674</t>
+          <t>1318; 11997</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1773; 11325</t>
+          <t>2227; 12051</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2368</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 10855</t>
+          <t>664; 7074</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 9794</t>
+          <t>666; 6693</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8218; 38177</t>
+          <t>15407; 36890</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6096; 16891</t>
+          <t>6448; 18308</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17238; 49429</t>
+          <t>25587; 50963</t>
         </is>
       </c>
     </row>
